--- a/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_SCF.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="296">
   <si>
     <t>Result</t>
   </si>
@@ -1315,6 +1315,99 @@
   </si>
   <si>
     <t>Fri Sep 18 02:21:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:53:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:57:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:59:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:01:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:03:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:17:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:19:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:21:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:24:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:26:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:33:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:35:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:38:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:40:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:42:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:45:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:48:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:55:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:57:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 16:59:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:10:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:18:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:21:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 20:24:16 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1759,7 +1852,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1907,7 +2000,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2050,7 +2143,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2193,7 +2286,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2338,7 +2431,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2482,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2625,7 +2718,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2768,7 +2861,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>243</v>
+        <v>291</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2910,7 +3003,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3055,7 +3148,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3198,7 +3291,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3341,7 +3434,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3457,7 +3550,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3599,7 +3692,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3744,7 +3837,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -3886,7 +3979,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4029,7 +4122,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4172,7 +4265,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4320,7 +4413,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4436,7 +4529,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4552,7 +4645,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4668,7 +4761,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4811,7 +4904,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -4954,7 +5047,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -5098,7 +5191,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
